--- a/bilibili_fans_data.xlsx
+++ b/bilibili_fans_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D464"/>
+  <dimension ref="A1:D465"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8674,6 +8674,24 @@
         <v>42913</v>
       </c>
     </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>18:24:29</t>
+        </is>
+      </c>
+      <c r="C465" t="n">
+        <v>203468</v>
+      </c>
+      <c r="D465" t="n">
+        <v>42907</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bilibili_fans_data.xlsx
+++ b/bilibili_fans_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D465"/>
+  <dimension ref="A1:D466"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8692,6 +8692,24 @@
         <v>42907</v>
       </c>
     </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>20:01:12</t>
+        </is>
+      </c>
+      <c r="C466" t="n">
+        <v>203449</v>
+      </c>
+      <c r="D466" t="n">
+        <v>42905</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bilibili_fans_data.xlsx
+++ b/bilibili_fans_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D466"/>
+  <dimension ref="A1:D467"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8710,6 +8710,24 @@
         <v>42905</v>
       </c>
     </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>19:21:25</t>
+        </is>
+      </c>
+      <c r="C467" t="n">
+        <v>203434</v>
+      </c>
+      <c r="D467" t="n">
+        <v>42899</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bilibili_fans_data.xlsx
+++ b/bilibili_fans_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D467"/>
+  <dimension ref="A1:D468"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8728,6 +8728,24 @@
         <v>42899</v>
       </c>
     </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>19:11:38</t>
+        </is>
+      </c>
+      <c r="C468" t="n">
+        <v>203416</v>
+      </c>
+      <c r="D468" t="n">
+        <v>42900</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bilibili_fans_data.xlsx
+++ b/bilibili_fans_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D468"/>
+  <dimension ref="A1:D469"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8746,6 +8746,24 @@
         <v>42900</v>
       </c>
     </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>19:23:32</t>
+        </is>
+      </c>
+      <c r="C469" t="n">
+        <v>203439</v>
+      </c>
+      <c r="D469" t="n">
+        <v>42896</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bilibili_fans_data.xlsx
+++ b/bilibili_fans_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D469"/>
+  <dimension ref="A1:D470"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8764,6 +8764,24 @@
         <v>42896</v>
       </c>
     </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>18:43:51</t>
+        </is>
+      </c>
+      <c r="C470" t="n">
+        <v>203444</v>
+      </c>
+      <c r="D470" t="n">
+        <v>42894</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bilibili_fans_data.xlsx
+++ b/bilibili_fans_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D470"/>
+  <dimension ref="A1:D471"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8782,6 +8782,24 @@
         <v>42894</v>
       </c>
     </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>18:16:38</t>
+        </is>
+      </c>
+      <c r="C471" t="n">
+        <v>203492</v>
+      </c>
+      <c r="D471" t="n">
+        <v>42889</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bilibili_fans_data.xlsx
+++ b/bilibili_fans_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D471"/>
+  <dimension ref="A1:D472"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8800,6 +8800,24 @@
         <v>42889</v>
       </c>
     </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>18:22:09</t>
+        </is>
+      </c>
+      <c r="C472" t="n">
+        <v>203493</v>
+      </c>
+      <c r="D472" t="n">
+        <v>42890</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bilibili_fans_data.xlsx
+++ b/bilibili_fans_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D472"/>
+  <dimension ref="A1:D473"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8818,6 +8818,24 @@
         <v>42890</v>
       </c>
     </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>20:11:02</t>
+        </is>
+      </c>
+      <c r="C473" t="n">
+        <v>203590</v>
+      </c>
+      <c r="D473" t="n">
+        <v>42889</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bilibili_fans_data.xlsx
+++ b/bilibili_fans_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D473"/>
+  <dimension ref="A1:D474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8836,6 +8836,24 @@
         <v>42889</v>
       </c>
     </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>19:21:54</t>
+        </is>
+      </c>
+      <c r="C474" t="n">
+        <v>203781</v>
+      </c>
+      <c r="D474" t="n">
+        <v>42893</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bilibili_fans_data.xlsx
+++ b/bilibili_fans_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D474"/>
+  <dimension ref="A1:D475"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8854,6 +8854,24 @@
         <v>42893</v>
       </c>
     </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>19:18:34</t>
+        </is>
+      </c>
+      <c r="C475" t="n">
+        <v>203771</v>
+      </c>
+      <c r="D475" t="n">
+        <v>42890</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bilibili_fans_data.xlsx
+++ b/bilibili_fans_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D475"/>
+  <dimension ref="A1:D476"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8872,6 +8872,24 @@
         <v>42890</v>
       </c>
     </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>19:35:53</t>
+        </is>
+      </c>
+      <c r="C476" t="n">
+        <v>203743</v>
+      </c>
+      <c r="D476" t="n">
+        <v>42882</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bilibili_fans_data.xlsx
+++ b/bilibili_fans_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D476"/>
+  <dimension ref="A1:D477"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8890,6 +8890,24 @@
         <v>42882</v>
       </c>
     </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>19:40:40</t>
+        </is>
+      </c>
+      <c r="C477" t="n">
+        <v>203717</v>
+      </c>
+      <c r="D477" t="n">
+        <v>42877</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bilibili_fans_data.xlsx
+++ b/bilibili_fans_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D477"/>
+  <dimension ref="A1:D478"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8908,6 +8908,24 @@
         <v>42877</v>
       </c>
     </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>18:49:38</t>
+        </is>
+      </c>
+      <c r="C478" t="n">
+        <v>203698</v>
+      </c>
+      <c r="D478" t="n">
+        <v>42873</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bilibili_fans_data.xlsx
+++ b/bilibili_fans_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D478"/>
+  <dimension ref="A1:D479"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8926,6 +8926,24 @@
         <v>42873</v>
       </c>
     </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>19:24:13</t>
+        </is>
+      </c>
+      <c r="C479" t="n">
+        <v>203686</v>
+      </c>
+      <c r="D479" t="n">
+        <v>42866</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bilibili_fans_data.xlsx
+++ b/bilibili_fans_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D479"/>
+  <dimension ref="A1:D480"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8944,6 +8944,24 @@
         <v>42866</v>
       </c>
     </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>21:27:37</t>
+        </is>
+      </c>
+      <c r="C480" t="n">
+        <v>203654</v>
+      </c>
+      <c r="D480" t="n">
+        <v>42864</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bilibili_fans_data.xlsx
+++ b/bilibili_fans_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D480"/>
+  <dimension ref="A1:D481"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8962,6 +8962,24 @@
         <v>42864</v>
       </c>
     </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>20:19:05</t>
+        </is>
+      </c>
+      <c r="C481" t="n">
+        <v>203624</v>
+      </c>
+      <c r="D481" t="n">
+        <v>42863</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bilibili_fans_data.xlsx
+++ b/bilibili_fans_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D481"/>
+  <dimension ref="A1:D482"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8980,6 +8980,24 @@
         <v>42863</v>
       </c>
     </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>20:23:28</t>
+        </is>
+      </c>
+      <c r="C482" t="n">
+        <v>203607</v>
+      </c>
+      <c r="D482" t="n">
+        <v>42860</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bilibili_fans_data.xlsx
+++ b/bilibili_fans_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D482"/>
+  <dimension ref="A1:D483"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8998,6 +8998,24 @@
         <v>42860</v>
       </c>
     </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>20:39:18</t>
+        </is>
+      </c>
+      <c r="C483" t="n">
+        <v>203590</v>
+      </c>
+      <c r="D483" t="n">
+        <v>42856</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bilibili_fans_data.xlsx
+++ b/bilibili_fans_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D483"/>
+  <dimension ref="A1:D484"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9016,6 +9016,24 @@
         <v>42856</v>
       </c>
     </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>20:13:59</t>
+        </is>
+      </c>
+      <c r="C484" t="n">
+        <v>203571</v>
+      </c>
+      <c r="D484" t="n">
+        <v>42853</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bilibili_fans_data.xlsx
+++ b/bilibili_fans_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D484"/>
+  <dimension ref="A1:D485"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9034,6 +9034,24 @@
         <v>42853</v>
       </c>
     </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>18:53:23</t>
+        </is>
+      </c>
+      <c r="C485" t="n">
+        <v>203570</v>
+      </c>
+      <c r="D485" t="n">
+        <v>42849</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bilibili_fans_data.xlsx
+++ b/bilibili_fans_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D485"/>
+  <dimension ref="A1:D486"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9052,6 +9052,24 @@
         <v>42849</v>
       </c>
     </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>18:53:03</t>
+        </is>
+      </c>
+      <c r="C486" t="n">
+        <v>203725</v>
+      </c>
+      <c r="D486" t="n">
+        <v>42845</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bilibili_fans_data.xlsx
+++ b/bilibili_fans_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D486"/>
+  <dimension ref="A1:D487"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9070,6 +9070,24 @@
         <v>42845</v>
       </c>
     </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>22:14:37</t>
+        </is>
+      </c>
+      <c r="C487" t="n">
+        <v>204206</v>
+      </c>
+      <c r="D487" t="n">
+        <v>42841</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bilibili_fans_data.xlsx
+++ b/bilibili_fans_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D487"/>
+  <dimension ref="A1:D488"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9088,6 +9088,24 @@
         <v>42841</v>
       </c>
     </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>20:38:20</t>
+        </is>
+      </c>
+      <c r="C488" t="n">
+        <v>204519</v>
+      </c>
+      <c r="D488" t="n">
+        <v>42840</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bilibili_fans_data.xlsx
+++ b/bilibili_fans_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D488"/>
+  <dimension ref="A1:D489"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9106,6 +9106,24 @@
         <v>42840</v>
       </c>
     </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>20:53:26</t>
+        </is>
+      </c>
+      <c r="C489" t="n">
+        <v>204621</v>
+      </c>
+      <c r="D489" t="n">
+        <v>42838</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bilibili_fans_data.xlsx
+++ b/bilibili_fans_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D489"/>
+  <dimension ref="A1:D490"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9124,6 +9124,24 @@
         <v>42838</v>
       </c>
     </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>20:54:30</t>
+        </is>
+      </c>
+      <c r="C490" t="n">
+        <v>204661</v>
+      </c>
+      <c r="D490" t="n">
+        <v>42831</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bilibili_fans_data.xlsx
+++ b/bilibili_fans_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D490"/>
+  <dimension ref="A1:D491"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9142,6 +9142,24 @@
         <v>42831</v>
       </c>
     </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>20:23:38</t>
+        </is>
+      </c>
+      <c r="C491" t="n">
+        <v>204823</v>
+      </c>
+      <c r="D491" t="n">
+        <v>42827</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bilibili_fans_data.xlsx
+++ b/bilibili_fans_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D491"/>
+  <dimension ref="A1:D492"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9160,6 +9160,24 @@
         <v>42827</v>
       </c>
     </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>19:37:44</t>
+        </is>
+      </c>
+      <c r="C492" t="n">
+        <v>204944</v>
+      </c>
+      <c r="D492" t="n">
+        <v>42824</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bilibili_fans_data.xlsx
+++ b/bilibili_fans_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D492"/>
+  <dimension ref="A1:D493"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9178,6 +9178,24 @@
         <v>42824</v>
       </c>
     </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>19:47:34</t>
+        </is>
+      </c>
+      <c r="C493" t="n">
+        <v>204928</v>
+      </c>
+      <c r="D493" t="n">
+        <v>42821</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bilibili_fans_data.xlsx
+++ b/bilibili_fans_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D493"/>
+  <dimension ref="A1:D494"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9196,6 +9196,24 @@
         <v>42821</v>
       </c>
     </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>22:39:05</t>
+        </is>
+      </c>
+      <c r="C494" t="n">
+        <v>204914</v>
+      </c>
+      <c r="D494" t="n">
+        <v>42817</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bilibili_fans_data.xlsx
+++ b/bilibili_fans_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D494"/>
+  <dimension ref="A1:D495"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9214,6 +9214,24 @@
         <v>42817</v>
       </c>
     </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>20:53:07</t>
+        </is>
+      </c>
+      <c r="C495" t="n">
+        <v>204902</v>
+      </c>
+      <c r="D495" t="n">
+        <v>42814</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bilibili_fans_data.xlsx
+++ b/bilibili_fans_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D495"/>
+  <dimension ref="A1:D496"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9232,6 +9232,24 @@
         <v>42814</v>
       </c>
     </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>19:49:29</t>
+        </is>
+      </c>
+      <c r="C496" t="n">
+        <v>204897</v>
+      </c>
+      <c r="D496" t="n">
+        <v>42815</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bilibili_fans_data.xlsx
+++ b/bilibili_fans_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D496"/>
+  <dimension ref="A1:D497"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9250,6 +9250,24 @@
         <v>42815</v>
       </c>
     </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>19:33:10</t>
+        </is>
+      </c>
+      <c r="C497" t="n">
+        <v>204892</v>
+      </c>
+      <c r="D497" t="n">
+        <v>42810</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bilibili_fans_data.xlsx
+++ b/bilibili_fans_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D497"/>
+  <dimension ref="A1:D498"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9268,6 +9268,24 @@
         <v>42810</v>
       </c>
     </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>19:07:17</t>
+        </is>
+      </c>
+      <c r="C498" t="n">
+        <v>204884</v>
+      </c>
+      <c r="D498" t="n">
+        <v>42805</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bilibili_fans_data.xlsx
+++ b/bilibili_fans_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D498"/>
+  <dimension ref="A1:D499"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9286,6 +9286,24 @@
         <v>42805</v>
       </c>
     </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>18:01:17</t>
+        </is>
+      </c>
+      <c r="C499" t="n">
+        <v>204874</v>
+      </c>
+      <c r="D499" t="n">
+        <v>42802</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bilibili_fans_data.xlsx
+++ b/bilibili_fans_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D499"/>
+  <dimension ref="A1:D500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9304,6 +9304,24 @@
         <v>42802</v>
       </c>
     </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>18:20:52</t>
+        </is>
+      </c>
+      <c r="C500" t="n">
+        <v>204872</v>
+      </c>
+      <c r="D500" t="n">
+        <v>42798</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bilibili_fans_data.xlsx
+++ b/bilibili_fans_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D500"/>
+  <dimension ref="A1:D501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9322,6 +9322,24 @@
         <v>42798</v>
       </c>
     </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>20:47:07</t>
+        </is>
+      </c>
+      <c r="C501" t="n">
+        <v>204853</v>
+      </c>
+      <c r="D501" t="n">
+        <v>42805</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bilibili_fans_data.xlsx
+++ b/bilibili_fans_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D501"/>
+  <dimension ref="A1:D502"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9340,6 +9340,24 @@
         <v>42805</v>
       </c>
     </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>19:43:16</t>
+        </is>
+      </c>
+      <c r="C502" t="n">
+        <v>204829</v>
+      </c>
+      <c r="D502" t="n">
+        <v>42802</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bilibili_fans_data.xlsx
+++ b/bilibili_fans_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D502"/>
+  <dimension ref="A1:D503"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9358,6 +9358,24 @@
         <v>42802</v>
       </c>
     </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>19:45:53</t>
+        </is>
+      </c>
+      <c r="C503" t="n">
+        <v>204799</v>
+      </c>
+      <c r="D503" t="n">
+        <v>42805</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bilibili_fans_data.xlsx
+++ b/bilibili_fans_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D503"/>
+  <dimension ref="A1:D504"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9376,6 +9376,24 @@
         <v>42805</v>
       </c>
     </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>19:36:23</t>
+        </is>
+      </c>
+      <c r="C504" t="n">
+        <v>204780</v>
+      </c>
+      <c r="D504" t="n">
+        <v>42801</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bilibili_fans_data.xlsx
+++ b/bilibili_fans_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D504"/>
+  <dimension ref="A1:D505"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9394,6 +9394,24 @@
         <v>42801</v>
       </c>
     </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>19:37:33</t>
+        </is>
+      </c>
+      <c r="C505" t="n">
+        <v>204786</v>
+      </c>
+      <c r="D505" t="n">
+        <v>42797</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bilibili_fans_data.xlsx
+++ b/bilibili_fans_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D505"/>
+  <dimension ref="A1:D506"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9412,6 +9412,24 @@
         <v>42797</v>
       </c>
     </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>18:26:13</t>
+        </is>
+      </c>
+      <c r="C506" t="n">
+        <v>204843</v>
+      </c>
+      <c r="D506" t="n">
+        <v>42798</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bilibili_fans_data.xlsx
+++ b/bilibili_fans_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D506"/>
+  <dimension ref="A1:D507"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9430,6 +9430,24 @@
         <v>42798</v>
       </c>
     </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>18:36:27</t>
+        </is>
+      </c>
+      <c r="C507" t="n">
+        <v>204879</v>
+      </c>
+      <c r="D507" t="n">
+        <v>42801</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bilibili_fans_data.xlsx
+++ b/bilibili_fans_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D507"/>
+  <dimension ref="A1:D508"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9448,6 +9448,24 @@
         <v>42801</v>
       </c>
     </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>20:47:57</t>
+        </is>
+      </c>
+      <c r="C508" t="n">
+        <v>204901</v>
+      </c>
+      <c r="D508" t="n">
+        <v>42809</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bilibili_fans_data.xlsx
+++ b/bilibili_fans_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D508"/>
+  <dimension ref="A1:D509"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9466,6 +9466,24 @@
         <v>42809</v>
       </c>
     </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>20:18:01</t>
+        </is>
+      </c>
+      <c r="C509" t="n">
+        <v>204907</v>
+      </c>
+      <c r="D509" t="n">
+        <v>42812</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bilibili_fans_data.xlsx
+++ b/bilibili_fans_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D509"/>
+  <dimension ref="A1:D510"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9484,6 +9484,24 @@
         <v>42812</v>
       </c>
     </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>20:40:24</t>
+        </is>
+      </c>
+      <c r="C510" t="n">
+        <v>204948</v>
+      </c>
+      <c r="D510" t="n">
+        <v>42815</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bilibili_fans_data.xlsx
+++ b/bilibili_fans_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D510"/>
+  <dimension ref="A1:D511"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9502,6 +9502,24 @@
         <v>42815</v>
       </c>
     </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>20:43:48</t>
+        </is>
+      </c>
+      <c r="C511" t="n">
+        <v>204953</v>
+      </c>
+      <c r="D511" t="n">
+        <v>42817</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bilibili_fans_data.xlsx
+++ b/bilibili_fans_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D511"/>
+  <dimension ref="A1:D512"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9520,6 +9520,24 @@
         <v>42817</v>
       </c>
     </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>20:15:15</t>
+        </is>
+      </c>
+      <c r="C512" t="n">
+        <v>205024</v>
+      </c>
+      <c r="D512" t="n">
+        <v>42840</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
